--- a/verification/cases/roundtrip/merge_cells/init.xlsx
+++ b/verification/cases/roundtrip/merge_cells/init.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="24030"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" autoCompressPictures="0"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{36D26B0E-DEAE-4D13-A4B6-E77BE5AA8984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="18380" tabRatio="500"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Merge" sheetId="1" r:id="rId1"/>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -83,6 +84,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -407,11 +416,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -423,13 +432,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -438,7 +447,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
